--- a/Generic MP3 Player Video Specification Sheet.xlsx
+++ b/Generic MP3 Player Video Specification Sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="83">
   <si>
     <t>URL</t>
   </si>
@@ -34,13 +34,22 @@
     <t>Video Size</t>
   </si>
   <si>
+    <t>Image Size</t>
+  </si>
+  <si>
     <t>Video Container</t>
   </si>
   <si>
     <t>Video Codec</t>
   </si>
   <si>
-    <t>Video Buffer Requirements</t>
+    <t>Optimal Video Parameters</t>
+  </si>
+  <si>
+    <t>Video Requirements</t>
+  </si>
+  <si>
+    <t>FFMPEG Version</t>
   </si>
   <si>
     <t>Video Transform</t>
@@ -58,6 +67,9 @@
     <t>Audio Rate</t>
   </si>
   <si>
+    <t>Image Format</t>
+  </si>
+  <si>
     <t>https://www.aliexpress.us/item/3256811470431948.html</t>
   </si>
   <si>
@@ -76,15 +88,27 @@
     <t>240x288</t>
   </si>
   <si>
+    <t>240x320</t>
+  </si>
+  <si>
     <t>AVI</t>
   </si>
   <si>
     <t>H.264</t>
   </si>
   <si>
-    <t>Buffer size: 2M
-Minimum QP: 12
-GOP: ~1 second</t>
+    <t>Bitrate: ~1-2 Mbps
+Minimum QP: 20
+GOP length: 1</t>
+  </si>
+  <si>
+    <t>Maximum bitrate: 10-20 Mbps
+Maximum I-frame/IDR: ~76 kb
+H.264 Baseline
+-bsf:v "filter_units=remove_types=6"</t>
+  </si>
+  <si>
+    <t>SetupPxConverter(2.0.10).exe</t>
   </si>
   <si>
     <t>Transpose cclock</t>
@@ -105,6 +129,10 @@
 8 kHz</t>
   </si>
   <si>
+    <t>JPEG
+BMP</t>
+  </si>
+  <si>
     <t>https://www.aliexpress.us/item/3256807720302915.html</t>
   </si>
   <si>
@@ -117,12 +145,10 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>240x240</t>
+  </si>
+  <si>
     <t xml:space="preserve">yuvj420p
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mono
-Stereo
 </t>
   </si>
   <si>
@@ -150,9 +176,15 @@
     <t>None</t>
   </si>
   <si>
-    <t xml:space="preserve">Transpose cclock
-Vertical flip
+    <t>Any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transpose clock
+Flip vertically
 </t>
+  </si>
+  <si>
+    <t>Stereo</t>
   </si>
   <si>
     <t xml:space="preserve">44.1 kHz
@@ -173,9 +205,6 @@
     <t>AGPTEK M6</t>
   </si>
   <si>
-    <t>240x320</t>
-  </si>
-  <si>
     <t>https://a.co/d/03RcQs66</t>
   </si>
   <si>
@@ -197,19 +226,45 @@
     <t>adpcm_ima_amv</t>
   </si>
   <si>
-    <t xml:space="preserve">Mono
-</t>
+    <t>Mono</t>
   </si>
   <si>
     <t>22.05 kHz</t>
   </si>
   <si>
+    <t>https://a.co/d/05aSR7W9</t>
+  </si>
+  <si>
+    <t>0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Samsung Galaxy Tab A7 Lite 8.7" 32GB WiFi Android Tablet, Compact, Portable, Slim Design, Kid Friendly, Sturdy Metal Frame, Expandable Storage, Long Lasting Battery, US Version, 2021, Gray </t>
+  </si>
+  <si>
+    <t>Galaxy Tab A7 Lite</t>
+  </si>
+  <si>
+    <t>800x1340</t>
+  </si>
+  <si>
+    <t>1340x800</t>
+  </si>
+  <si>
+    <t>MP4</t>
+  </si>
+  <si>
+    <t>yuv240p</t>
+  </si>
+  <si>
+    <t>AAC Low</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
     <t>https://a.co/d/03ihdjUI</t>
   </si>
   <si>
-    <t>0006</t>
-  </si>
-  <si>
     <t xml:space="preserve">RUIZU 96GB MP3 Player with Bluetooth 5.0, Portable Digital Music Player with FM Radio, Voice Recorder, E-Book Reader, Video, Pedometer, Alarm Clock, Supports up to 128GB Micro SD Card </t>
   </si>
   <si>
@@ -217,9 +272,6 @@
   </si>
   <si>
     <t>https://a.co/d/0iGzQf9p</t>
-  </si>
-  <si>
-    <t>0007</t>
   </si>
   <si>
     <t xml:space="preserve">RUIZU 64GB MP3 Player with Bluetooth 5.3, Portable Music Player for Kids Sports Running, FM Radio, Voice Recorder, Equalizer, 80H Digital Audio Video Shuffle Resume Playback, Up to 128GB Micro SD Card </t>
@@ -368,7 +420,7 @@
     <xdr:ext cx="962025" cy="962025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -396,7 +448,7 @@
     <xdr:ext cx="962025" cy="962025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -424,7 +476,7 @@
     <xdr:ext cx="962025" cy="962025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image8.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -452,7 +504,7 @@
     <xdr:ext cx="962025" cy="1000125"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -480,7 +532,7 @@
     <xdr:ext cx="962025" cy="942975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -505,10 +557,10 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="962025" cy="981075"/>
+    <xdr:ext cx="838200" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -533,6 +585,34 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
+    <xdr:ext cx="962025" cy="981075"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
     <xdr:ext cx="962025" cy="952500"/>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -540,7 +620,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -562,8 +642,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O8" displayName="Table1" name="Table1" id="1">
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S9" displayName="Table1" name="Table1" id="1">
+  <tableColumns count="19">
     <tableColumn name="URL" id="1"/>
     <tableColumn name="UID" id="2"/>
     <tableColumn name="Image" id="3"/>
@@ -571,14 +651,18 @@
     <tableColumn name="Name" id="5"/>
     <tableColumn name="Display Size" id="6"/>
     <tableColumn name="Video Size" id="7"/>
-    <tableColumn name="Video Container" id="8"/>
-    <tableColumn name="Video Codec" id="9"/>
-    <tableColumn name="Video Buffer Requirements" id="10"/>
-    <tableColumn name="Video Transform" id="11"/>
-    <tableColumn name="Pixel Format" id="12"/>
-    <tableColumn name="Audio Codec" id="13"/>
-    <tableColumn name="Audio Channels" id="14"/>
-    <tableColumn name="Audio Rate" id="15"/>
+    <tableColumn name="Image Size" id="8"/>
+    <tableColumn name="Video Container" id="9"/>
+    <tableColumn name="Video Codec" id="10"/>
+    <tableColumn name="Optimal Video Parameters" id="11"/>
+    <tableColumn name="Video Requirements" id="12"/>
+    <tableColumn name="FFMPEG Version" id="13"/>
+    <tableColumn name="Video Transform" id="14"/>
+    <tableColumn name="Pixel Format" id="15"/>
+    <tableColumn name="Audio Codec" id="16"/>
+    <tableColumn name="Audio Channels" id="17"/>
+    <tableColumn name="Audio Rate" id="18"/>
+    <tableColumn name="Image Format" id="19"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -788,8 +872,8 @@
     <col customWidth="1" min="1" max="1" width="7.88"/>
     <col customWidth="1" min="4" max="4" width="37.63"/>
     <col customWidth="1" min="6" max="6" width="14.38"/>
-    <col customWidth="1" min="7" max="7" width="13.25"/>
-    <col customWidth="1" min="8" max="15" width="14.88"/>
+    <col customWidth="1" min="7" max="8" width="13.25"/>
+    <col customWidth="1" min="9" max="19" width="14.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -817,286 +901,411 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="112.5" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="112.5" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="6" t="s">
+      <c r="O3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>35</v>
+      <c r="R3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="112.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>43</v>
+      <c r="Q4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="112.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="112.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>57</v>
+        <v>42</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="112.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="112.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>63</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>65</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" ht="112.5" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:B8"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:B9"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="A2"/>
@@ -1106,10 +1315,11 @@
     <hyperlink r:id="rId5" ref="A6"/>
     <hyperlink r:id="rId6" ref="A7"/>
     <hyperlink r:id="rId7" ref="A8"/>
+    <hyperlink r:id="rId8" ref="A9"/>
   </hyperlinks>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>